--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CAJA RURAL DE ZAMORA CBCV BOECILLO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CAJA RURAL DE ZAMORA CBCV BOECILLO.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>34.2805</v>
+        <v>5.7277</v>
       </c>
       <c r="E2" t="n">
-        <v>29.6053</v>
+        <v>5.982100000000002</v>
       </c>
       <c r="F2" t="n">
-        <v>4.674999999999999</v>
+        <v>-0.2544</v>
       </c>
       <c r="G2" t="n">
         <v>-29.6592</v>
@@ -610,13 +610,13 @@
         <v>54.6212</v>
       </c>
       <c r="S2" t="n">
-        <v>36.7724</v>
+        <v>8.2196</v>
       </c>
       <c r="T2" t="n">
-        <v>27.9938</v>
+        <v>4.3708</v>
       </c>
       <c r="U2" t="n">
-        <v>8.7784</v>
+        <v>3.8489</v>
       </c>
       <c r="V2" t="n">
         <v>12.3057</v>
@@ -643,13 +643,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.3851</v>
+        <v>-0.8708999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3396000000000001</v>
+        <v>0.6401000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.7249</v>
+        <v>-1.511</v>
       </c>
       <c r="G3" t="n">
         <v>-0.8742000000000001</v>
@@ -688,13 +688,13 @@
         <v>0.772</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2829</v>
+        <v>-0.7686999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5949</v>
+        <v>-0.2945</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.4743</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.4447</v>
+        <v>-1.518</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0136</v>
+        <v>-0.1137</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4311</v>
+        <v>-1.4043</v>
       </c>
       <c r="G4" t="n">
         <v>-1.6106</v>
@@ -766,13 +766,13 @@
         <v>0.193</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0271</v>
+        <v>-0.1005</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4891</v>
+        <v>0.389</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5162</v>
+        <v>-0.4895</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. BARNES HERNANDEZ</t>
+          <t>A. GOMEZ RAMOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.7582</v>
+        <v>-3.8776</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5151</v>
+        <v>0.04150000000000009</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2431</v>
+        <v>-3.919</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.715199999999999</v>
+        <v>-4.2088</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.201099999999999</v>
+        <v>-4.3209</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4858</v>
+        <v>0.1121000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>7.6628</v>
+        <v>2.1801</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9931</v>
+        <v>0.9676</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6698</v>
+        <v>1.2124</v>
       </c>
       <c r="M5" t="n">
-        <v>-9.3779</v>
+        <v>-6.3889</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.194099999999999</v>
+        <v>-5.2885</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1838</v>
+        <v>-1.1003</v>
       </c>
       <c r="P5" t="n">
-        <v>1.351</v>
+        <v>2.1231</v>
       </c>
       <c r="Q5" t="n">
-        <v>-8.878299999999999</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>10.2294</v>
+        <v>4.0532</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4315999999999998</v>
+        <v>-0.9343</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0553</v>
+        <v>-0.2085</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6233999999999998</v>
+        <v>-0.7258</v>
       </c>
       <c r="V5" t="n">
-        <v>-3.8256</v>
+        <v>-0.8576</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.3547</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.4709</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GOMEZ RAMOS</t>
+          <t>A. DEL VAL IBAÑEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.685700000000001</v>
+        <v>-4.8019</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6595</v>
+        <v>1.5677</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.026199999999999</v>
+        <v>-6.369499999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.2088</v>
+        <v>-3.9834</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.3209</v>
+        <v>-1.0773</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1121000000000001</v>
+        <v>-2.906</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1801</v>
+        <v>1.4296</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9676</v>
+        <v>2.0079</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2124</v>
+        <v>-0.5783</v>
       </c>
       <c r="M6" t="n">
-        <v>-6.3889</v>
+        <v>-5.4128</v>
       </c>
       <c r="N6" t="n">
-        <v>-5.2885</v>
+        <v>-3.0851</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1003</v>
+        <v>-2.3277</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1231</v>
+        <v>1.351</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.0532</v>
+        <v>1.351</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7424</v>
+        <v>-1.8416</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9095</v>
+        <v>-0.4335</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8329</v>
+        <v>-1.4079</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.8576</v>
+        <v>-0.3281</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8576</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. DE LARREA ASENJO</t>
+          <t>R. HERNANSANZ HERRERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.375999999999999</v>
+        <v>-4.8483</v>
       </c>
       <c r="E7" t="n">
-        <v>5.418799999999998</v>
+        <v>-4.0486</v>
       </c>
       <c r="F7" t="n">
-        <v>-10.7947</v>
+        <v>-0.7997000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-11.5911</v>
+        <v>-3.4151</v>
       </c>
       <c r="H7" t="n">
-        <v>-8.370000000000001</v>
+        <v>-3.6235</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.221</v>
+        <v>0.2084</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8044000000000004</v>
+        <v>-2.1129</v>
       </c>
       <c r="K7" t="n">
-        <v>2.0275</v>
+        <v>-1.5267</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2229</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-12.3956</v>
+        <v>-1.3022</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.3977</v>
+        <v>-2.0968</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9979</v>
+        <v>0.7946</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1929000000000001</v>
+        <v>-0.772</v>
       </c>
       <c r="Q7" t="n">
-        <v>-11.1943</v>
+        <v>-1.544</v>
       </c>
       <c r="R7" t="n">
-        <v>11.3875</v>
+        <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7431</v>
+        <v>-0.3754</v>
       </c>
       <c r="T7" t="n">
-        <v>3.4122</v>
+        <v>-0.3915999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.669</v>
+        <v>0.01619999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>4.279</v>
+        <v>-0.2859</v>
       </c>
       <c r="W7" t="n">
-        <v>12.3965</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-8.1175</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DEL VAL IBAÑEZ</t>
+          <t>L. BARNES HERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.6029</v>
+        <v>-5.7494</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7665</v>
+        <v>-3.3991</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.3696</v>
+        <v>-2.3504</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.9834</v>
+        <v>-1.715199999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0773</v>
+        <v>-3.201099999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.906</v>
+        <v>1.4858</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4296</v>
+        <v>7.6628</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0079</v>
+        <v>4.9931</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5783</v>
+        <v>2.6698</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.4128</v>
+        <v>-9.3779</v>
       </c>
       <c r="N8" t="n">
-        <v>-3.0851</v>
+        <v>-8.194099999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.3277</v>
+        <v>-1.1838</v>
       </c>
       <c r="P8" t="n">
         <v>1.351</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-8.878299999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>1.351</v>
+        <v>10.2294</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.6426</v>
+        <v>-1.5597</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2347</v>
+        <v>-0.8287</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4078</v>
+        <v>-0.7308</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3281</v>
+        <v>-3.8256</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5717</v>
+        <v>-1.3547</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8999</v>
+        <v>-2.4709</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. HERNANSANZ HERRERO</t>
+          <t>M. DE LARREA ASENJO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.6488</v>
+        <v>-6.7126</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.608700000000001</v>
+        <v>3.575500000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0401</v>
+        <v>-10.288</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4151</v>
+        <v>-11.5911</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.6235</v>
+        <v>-8.370000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2084</v>
+        <v>-3.221</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1129</v>
+        <v>0.8044000000000004</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.5267</v>
+        <v>2.0275</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-1.2229</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3022</v>
+        <v>-12.3956</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0968</v>
+        <v>-10.3977</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7946</v>
+        <v>-1.9979</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.772</v>
+        <v>0.1929000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.544</v>
+        <v>-11.1943</v>
       </c>
       <c r="R9" t="n">
-        <v>0.772</v>
+        <v>11.3875</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1759</v>
+        <v>0.4066</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9518</v>
+        <v>1.5692</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.224</v>
+        <v>-1.1625</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2859</v>
+        <v>4.279</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>12.3965</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2859</v>
+        <v>-8.1175</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>-10.1715</v>
+        <v>-9.633599999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.092</v>
+        <v>-2.472399999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.0794</v>
+        <v>-7.1613</v>
       </c>
       <c r="G10" t="n">
         <v>5.155000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>17.5638</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2906999999999998</v>
+        <v>0.2467000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.9073</v>
+        <v>-1.2877</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6164</v>
+        <v>1.5345</v>
       </c>
       <c r="V10" t="n">
         <v>-11.9476</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. MUZQUIZ GURREA</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.3818</v>
+        <v>-11.6418</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4756</v>
+        <v>-14.5088</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.9063</v>
+        <v>2.8674</v>
       </c>
       <c r="G11" t="n">
-        <v>-21.4515</v>
+        <v>-39.5254</v>
       </c>
       <c r="H11" t="n">
-        <v>-14.0007</v>
+        <v>-25.6004</v>
       </c>
       <c r="I11" t="n">
-        <v>-7.4509</v>
+        <v>-13.9248</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.7259</v>
+        <v>-5.695600000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.4714</v>
+        <v>0.6125999999999997</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2544</v>
+        <v>-6.307700000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-14.7254</v>
+        <v>-33.8298</v>
       </c>
       <c r="N11" t="n">
-        <v>-8.529200000000001</v>
+        <v>-26.213</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.196300000000001</v>
+        <v>-7.6168</v>
       </c>
       <c r="P11" t="n">
-        <v>10.2294</v>
+        <v>19.1078</v>
       </c>
       <c r="Q11" t="n">
-        <v>-11.5802</v>
+        <v>-26.4418</v>
       </c>
       <c r="R11" t="n">
-        <v>21.8098</v>
+        <v>45.55</v>
       </c>
       <c r="S11" t="n">
-        <v>12.0388</v>
+        <v>-5.6908</v>
       </c>
       <c r="T11" t="n">
-        <v>9.601900000000001</v>
+        <v>-4.5916</v>
       </c>
       <c r="U11" t="n">
-        <v>2.4369</v>
+        <v>-1.0993</v>
       </c>
       <c r="V11" t="n">
-        <v>-11.1985</v>
+        <v>14.4667</v>
       </c>
       <c r="W11" t="n">
-        <v>3.2291</v>
+        <v>22.2204</v>
       </c>
       <c r="X11" t="n">
-        <v>-14.4277</v>
+        <v>-7.7538</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.8338</v>
+        <v>-12.3999</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.507299999999999</v>
+        <v>-9.832599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3264</v>
+        <v>-2.5673</v>
       </c>
       <c r="G12" t="n">
         <v>-7.3209</v>
@@ -1390,13 +1390,13 @@
         <v>13.3176</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3604</v>
+        <v>-2.9266</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3363</v>
+        <v>-1.6616</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.024</v>
+        <v>-1.2649</v>
       </c>
       <c r="V12" t="n">
         <v>1.1285</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. POPA ANDREI</t>
+          <t>P. HERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.6633</v>
+        <v>-13.2172</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.019900000000002</v>
+        <v>-11.763</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.643400000000002</v>
+        <v>-1.454</v>
       </c>
       <c r="G13" t="n">
-        <v>-41.6666</v>
+        <v>-3.0158</v>
       </c>
       <c r="H13" t="n">
-        <v>-28.8444</v>
+        <v>-2.5715</v>
       </c>
       <c r="I13" t="n">
-        <v>-12.8224</v>
+        <v>-0.4440999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8545</v>
+        <v>3.8432</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1487</v>
+        <v>6.8662</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2943000000000005</v>
+        <v>-3.0228</v>
       </c>
       <c r="M13" t="n">
-        <v>-46.5211</v>
+        <v>-6.858700000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-33.9932</v>
+        <v>-9.4376</v>
       </c>
       <c r="O13" t="n">
-        <v>-12.5277</v>
+        <v>2.5789</v>
       </c>
       <c r="P13" t="n">
-        <v>16.7917</v>
+        <v>5.5971</v>
       </c>
       <c r="Q13" t="n">
-        <v>-40.7244</v>
+        <v>-16.4055</v>
       </c>
       <c r="R13" t="n">
-        <v>57.5166</v>
+        <v>22.0027</v>
       </c>
       <c r="S13" t="n">
-        <v>2.13</v>
+        <v>-4.730300000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>5.1</v>
+        <v>-3.3293</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.9698</v>
+        <v>-1.4012</v>
       </c>
       <c r="V13" t="n">
-        <v>7.082000000000001</v>
+        <v>-11.0687</v>
       </c>
       <c r="W13" t="n">
-        <v>24.7509</v>
+        <v>4.1291</v>
       </c>
       <c r="X13" t="n">
-        <v>-17.6692</v>
+        <v>-15.1977</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ BLANCO</t>
+          <t>J. RODRIGUEZ NERI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.7478</v>
+        <v>-17.5461</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.1806</v>
+        <v>-13.3558</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.567200000000001</v>
+        <v>-4.1905</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.0158</v>
+        <v>0.5833999999999993</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.5715</v>
+        <v>-4.153399999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4440999999999999</v>
+        <v>4.737</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8432</v>
+        <v>20.4791</v>
       </c>
       <c r="K14" t="n">
-        <v>6.8662</v>
+        <v>14.3783</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.0228</v>
+        <v>6.1007</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.858700000000001</v>
+        <v>-19.8956</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.4376</v>
+        <v>-18.5317</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5789</v>
+        <v>-1.3639</v>
       </c>
       <c r="P14" t="n">
-        <v>5.5971</v>
+        <v>-18.9146</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.4055</v>
+        <v>-44.1988</v>
       </c>
       <c r="R14" t="n">
-        <v>22.0027</v>
+        <v>25.2842</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.2608</v>
+        <v>-2.8585</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.7469</v>
+        <v>-1.503</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5139</v>
+        <v>-1.3554</v>
       </c>
       <c r="V14" t="n">
-        <v>-11.0687</v>
+        <v>3.6435</v>
       </c>
       <c r="W14" t="n">
-        <v>4.1291</v>
+        <v>11.8672</v>
       </c>
       <c r="X14" t="n">
-        <v>-15.1977</v>
+        <v>-8.223600000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ NERI</t>
+          <t>D. MUZQUIZ GURREA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
-        <v>-20.2771</v>
+        <v>-18.8118</v>
       </c>
       <c r="E15" t="n">
-        <v>-15.7125</v>
+        <v>-11.7903</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.564399999999999</v>
+        <v>-7.0218</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5833999999999993</v>
+        <v>-21.4515</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.153399999999999</v>
+        <v>-14.0007</v>
       </c>
       <c r="I15" t="n">
-        <v>4.737</v>
+        <v>-7.4509</v>
       </c>
       <c r="J15" t="n">
-        <v>20.4791</v>
+        <v>-6.7259</v>
       </c>
       <c r="K15" t="n">
-        <v>14.3783</v>
+        <v>-5.4714</v>
       </c>
       <c r="L15" t="n">
-        <v>6.1007</v>
+        <v>-1.2544</v>
       </c>
       <c r="M15" t="n">
-        <v>-19.8956</v>
+        <v>-14.7254</v>
       </c>
       <c r="N15" t="n">
-        <v>-18.5317</v>
+        <v>-8.529200000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3639</v>
+        <v>-6.196300000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-18.9146</v>
+        <v>10.2294</v>
       </c>
       <c r="Q15" t="n">
-        <v>-44.1988</v>
+        <v>-11.5802</v>
       </c>
       <c r="R15" t="n">
-        <v>25.2842</v>
+        <v>21.8098</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.5893</v>
+        <v>3.6083</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.8599</v>
+        <v>3.2872</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.7296</v>
+        <v>0.3213000000000003</v>
       </c>
       <c r="V15" t="n">
-        <v>3.6435</v>
+        <v>-11.1985</v>
       </c>
       <c r="W15" t="n">
-        <v>11.8672</v>
+        <v>3.2291</v>
       </c>
       <c r="X15" t="n">
-        <v>-8.223600000000001</v>
+        <v>-14.4277</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. POPA ANDREI</t>
+          <t>J. LAMBAS VIVANCOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-22.0977</v>
+        <v>-20.2428</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.7443</v>
+        <v>-3.414600000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-9.353200000000001</v>
+        <v>-16.828</v>
       </c>
       <c r="G16" t="n">
-        <v>-37.091</v>
+        <v>-5.7986</v>
       </c>
       <c r="H16" t="n">
-        <v>-26.7769</v>
+        <v>-15.6237</v>
       </c>
       <c r="I16" t="n">
-        <v>-10.314</v>
+        <v>9.824999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1.217299999999999</v>
+        <v>27.6026</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6908999999999996</v>
+        <v>9.988900000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5266999999999999</v>
+        <v>17.614</v>
       </c>
       <c r="M16" t="n">
-        <v>-38.3084</v>
+        <v>-33.4014</v>
       </c>
       <c r="N16" t="n">
-        <v>-27.4675</v>
+        <v>-25.6125</v>
       </c>
       <c r="O16" t="n">
-        <v>-10.8406</v>
+        <v>-7.7889</v>
       </c>
       <c r="P16" t="n">
-        <v>20.8446</v>
+        <v>-0.3859999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-18.3356</v>
+        <v>-41.1106</v>
       </c>
       <c r="R16" t="n">
-        <v>39.1805</v>
+        <v>40.7246</v>
       </c>
       <c r="S16" t="n">
-        <v>-6.7684</v>
+        <v>-9.659000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.4544</v>
+        <v>-4.0187</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.3143</v>
+        <v>-5.6406</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9166000000000003</v>
+        <v>-4.3993</v>
       </c>
       <c r="W16" t="n">
-        <v>6.8285</v>
+        <v>14.112</v>
       </c>
       <c r="X16" t="n">
-        <v>-5.912</v>
+        <v>-18.5112</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>S. POPA ANDREI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-24.2818</v>
+        <v>-20.6782</v>
       </c>
       <c r="E17" t="n">
-        <v>-24.3949</v>
+        <v>-11.2701</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1134000000000006</v>
+        <v>-9.408100000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-39.5254</v>
+        <v>-37.091</v>
       </c>
       <c r="H17" t="n">
-        <v>-25.6004</v>
+        <v>-26.7769</v>
       </c>
       <c r="I17" t="n">
-        <v>-13.9248</v>
+        <v>-10.314</v>
       </c>
       <c r="J17" t="n">
-        <v>-5.695600000000001</v>
+        <v>1.217299999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6125999999999997</v>
+        <v>0.6908999999999996</v>
       </c>
       <c r="L17" t="n">
-        <v>-6.307700000000001</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-33.8298</v>
+        <v>-38.3084</v>
       </c>
       <c r="N17" t="n">
-        <v>-26.213</v>
+        <v>-27.4675</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.6168</v>
+        <v>-10.8406</v>
       </c>
       <c r="P17" t="n">
-        <v>19.1078</v>
+        <v>20.8446</v>
       </c>
       <c r="Q17" t="n">
-        <v>-26.4418</v>
+        <v>-18.3356</v>
       </c>
       <c r="R17" t="n">
-        <v>45.55</v>
+        <v>39.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>-18.3308</v>
+        <v>-5.3489</v>
       </c>
       <c r="T17" t="n">
-        <v>-14.4778</v>
+        <v>-0.98</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.8538</v>
+        <v>-4.3689</v>
       </c>
       <c r="V17" t="n">
-        <v>14.4667</v>
+        <v>0.9166000000000003</v>
       </c>
       <c r="W17" t="n">
-        <v>22.2204</v>
+        <v>6.8285</v>
       </c>
       <c r="X17" t="n">
-        <v>-7.7538</v>
+        <v>-5.912</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>22</v>
       </c>
       <c r="D18" t="n">
-        <v>-28.7779</v>
+        <v>-20.7447</v>
       </c>
       <c r="E18" t="n">
-        <v>-17.9385</v>
+        <v>-13.5978</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.8393</v>
+        <v>-7.146899999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-18.6804</v>
@@ -1858,13 +1858,13 @@
         <v>35.1276</v>
       </c>
       <c r="S18" t="n">
-        <v>-13.9749</v>
+        <v>-5.942</v>
       </c>
       <c r="T18" t="n">
-        <v>-6.852600000000001</v>
+        <v>-2.5119</v>
       </c>
       <c r="U18" t="n">
-        <v>-7.1224</v>
+        <v>-3.4299</v>
       </c>
       <c r="V18" t="n">
         <v>-5.5797</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LAMBAS VIVANCOS</t>
+          <t>R. POPA ANDREI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-34.5178</v>
+        <v>-23.4715</v>
       </c>
       <c r="E19" t="n">
-        <v>-14.4807</v>
+        <v>-12.7004</v>
       </c>
       <c r="F19" t="n">
-        <v>-20.0366</v>
+        <v>-10.7708</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.7986</v>
+        <v>-41.6666</v>
       </c>
       <c r="H19" t="n">
-        <v>-15.6237</v>
+        <v>-28.8444</v>
       </c>
       <c r="I19" t="n">
-        <v>9.824999999999999</v>
+        <v>-12.8224</v>
       </c>
       <c r="J19" t="n">
-        <v>27.6026</v>
+        <v>4.8545</v>
       </c>
       <c r="K19" t="n">
-        <v>9.988900000000001</v>
+        <v>5.1487</v>
       </c>
       <c r="L19" t="n">
-        <v>17.614</v>
+        <v>-0.2943000000000005</v>
       </c>
       <c r="M19" t="n">
-        <v>-33.4014</v>
+        <v>-46.5211</v>
       </c>
       <c r="N19" t="n">
-        <v>-25.6125</v>
+        <v>-33.9932</v>
       </c>
       <c r="O19" t="n">
-        <v>-7.7889</v>
+        <v>-12.5277</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3859999999999999</v>
+        <v>16.7917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-41.1106</v>
+        <v>-40.7244</v>
       </c>
       <c r="R19" t="n">
-        <v>40.7246</v>
+        <v>57.5166</v>
       </c>
       <c r="S19" t="n">
-        <v>-23.9339</v>
+        <v>-5.6782</v>
       </c>
       <c r="T19" t="n">
-        <v>-15.0845</v>
+        <v>-1.5808</v>
       </c>
       <c r="U19" t="n">
-        <v>-8.8491</v>
+        <v>-4.0974</v>
       </c>
       <c r="V19" t="n">
-        <v>-4.3993</v>
+        <v>7.082000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>14.112</v>
+        <v>24.7509</v>
       </c>
       <c r="X19" t="n">
-        <v>-18.5112</v>
+        <v>-17.6692</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>-54.7236</v>
+        <v>-41.1422</v>
       </c>
       <c r="E20" t="n">
-        <v>-30.0693</v>
+        <v>-20.8216</v>
       </c>
       <c r="F20" t="n">
-        <v>-24.6542</v>
+        <v>-20.3207</v>
       </c>
       <c r="G20" t="n">
         <v>-30.7855</v>
@@ -2014,13 +2014,13 @@
         <v>38.7947</v>
       </c>
       <c r="S20" t="n">
-        <v>-23.1669</v>
+        <v>-9.5854</v>
       </c>
       <c r="T20" t="n">
-        <v>-14.5345</v>
+        <v>-5.2868</v>
       </c>
       <c r="U20" t="n">
-        <v>-8.6325</v>
+        <v>-4.2985</v>
       </c>
       <c r="V20" t="n">
         <v>-14.6681</v>
@@ -2047,13 +2047,13 @@
         <v>18</v>
       </c>
       <c r="D21" t="n">
-        <v>-70.0562</v>
+        <v>-60.3273</v>
       </c>
       <c r="E21" t="n">
-        <v>-58.3116</v>
+        <v>-51.6865</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.7446</v>
+        <v>-8.641</v>
       </c>
       <c r="G21" t="n">
         <v>-42.3756</v>
@@ -2092,13 +2092,13 @@
         <v>28.7583</v>
       </c>
       <c r="S21" t="n">
-        <v>-19.8381</v>
+        <v>-10.1094</v>
       </c>
       <c r="T21" t="n">
-        <v>-11.67</v>
+        <v>-5.0449</v>
       </c>
       <c r="U21" t="n">
-        <v>-8.167999999999999</v>
+        <v>-5.0645</v>
       </c>
       <c r="V21" t="n">
         <v>-6.2983</v>
@@ -2125,13 +2125,13 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>-313.1512</v>
+        <v>-292.5081</v>
       </c>
       <c r="E22" t="n">
-        <v>-181.5939</v>
+        <v>-172.9684</v>
       </c>
       <c r="F22" t="n">
-        <v>-131.5563</v>
+        <v>-119.5393</v>
       </c>
       <c r="G22" t="n">
         <v>-299.0305</v>
@@ -2140,10 +2140,10 @@
         <v>-199.2598</v>
       </c>
       <c r="I22" t="n">
-        <v>-99.76949999999999</v>
+        <v>-99.76950000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>87.41820000000003</v>
+        <v>87.41820000000001</v>
       </c>
       <c r="K22" t="n">
         <v>98.96360000000001</v>
@@ -2161,7 +2161,7 @@
         <v>-88.2234</v>
       </c>
       <c r="P22" t="n">
-        <v>88.78309999999999</v>
+        <v>88.7831</v>
       </c>
       <c r="Q22" t="n">
         <v>-380.223</v>
@@ -2170,13 +2170,13 @@
         <v>469.0097</v>
       </c>
       <c r="S22" t="n">
-        <v>-76.2692</v>
+        <v>-55.6281</v>
       </c>
       <c r="T22" t="n">
-        <v>-32.9628</v>
+        <v>-24.3369</v>
       </c>
       <c r="U22" t="n">
-        <v>-43.307</v>
+        <v>-31.2905</v>
       </c>
       <c r="V22" t="n">
         <v>-26.6354</v>
